--- a/naver-place-crawler/results_health/광주_PT.xlsx
+++ b/naver-place-crawler/results_health/광주_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에스짐문흥점 24시 헬스PT</t>
+          <t>짐플릭스 첨단점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sgym13@naver.com</t>
+          <t>gymflix@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1369-6135</t>
+          <t>0507-1364-2795</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>광주 북구 서하로 372 4층 SGYM 문흥점</t>
+          <t>광주광역시 광산구 임방울대로800번길 72 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgym13/223494722999</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,19 +601,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5u0r4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="Q2" t="n">
-        <v>118</v>
+        <v>885</v>
       </c>
       <c r="R2" t="n">
-        <v>394</v>
+        <v>1156</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1265291164</t>
+          <t>1955578541</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1265291164</t>
+          <t>https://m.place.naver.com/place/1955578541</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>매곡동 헬스 최달봉 PT</t>
+          <t>24시 평생헬스 신창점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wetang@naver.com</t>
+          <t>aldusl7901@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1337-0171</t>
+          <t>0507-1420-8259</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>광주 북구 서하로106번길 6 2층</t>
+          <t>광주광역시 광산구 북문대로 431 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/choi_dal_bong_pt</t>
+          <t>https://www.instagram.com/forlifegym_shinchang/profilecard/?igsh=MTNyanVuZHVoaHNvcg==</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w0u7jl4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>30</v>
+        <v>477</v>
       </c>
       <c r="Q3" t="n">
-        <v>41</v>
+        <v>378</v>
       </c>
       <c r="R3" t="n">
-        <v>71</v>
+        <v>855</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>388902640</t>
+          <t>1082086454</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/388902640</t>
+          <t>https://m.place.naver.com/place/1082086454</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -755,12 +747,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>짐플릭스 첨단점</t>
+          <t>짐플릭스 수완점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -771,13 +763,13 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1364-2795</t>
+          <t>0507-1383-2795</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>광주 광산구 임방울대로800번길 72 3층</t>
+          <t>광주광역시 광산구 임방울대로 342 8층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wkfba0h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="Q4" t="n">
-        <v>888</v>
+        <v>749</v>
       </c>
       <c r="R4" t="n">
-        <v>1159</v>
+        <v>1003</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1955578541</t>
+          <t>1999324427</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1955578541</t>
+          <t>https://m.place.naver.com/place/1999324427</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -853,34 +841,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24시 평생헬스 신창점</t>
+          <t>평생헬스 쌍촌점 해머스트렝스오피셜센터 PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>aldusl7901@naver.com</t>
+          <t>ssanglifegym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1420-8259</t>
+          <t>0507-1401-7847</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>광주 광산구 북문대로 431 1층</t>
+          <t>광주광역시 서구 상무대로956번길 6 . 지하 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forlifegym_shinchang/profilecard/?igsh=MTNyanVuZHVoaHNvcg==</t>
+          <t>https://blog.naver.com/ssanglifegym</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -915,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>475</v>
+        <v>264</v>
       </c>
       <c r="Q5" t="n">
-        <v>378</v>
+        <v>555</v>
       </c>
       <c r="R5" t="n">
-        <v>853</v>
+        <v>819</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1082086454</t>
+          <t>1777617878</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1082086454</t>
+          <t>https://m.place.naver.com/place/1777617878</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -947,12 +935,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>짐플릭스 수완점</t>
+          <t>짐플릭스 봉선점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -963,13 +951,13 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1383-2795</t>
+          <t>0507-1307-2795</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>광주 광산구 임방울대로 342 8층</t>
+          <t>광주광역시 남구 봉선로 205 4층 짐플릭스 봉선점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wkfba0h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>254</v>
+        <v>217</v>
       </c>
       <c r="Q6" t="n">
-        <v>755</v>
+        <v>781</v>
       </c>
       <c r="R6" t="n">
-        <v>1009</v>
+        <v>998</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1999324427</t>
+          <t>1250527936</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1999324427</t>
+          <t>https://m.place.naver.com/place/1250527936</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1045,39 +1029,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>평생헬스 쌍촌점 해머스트렝스오피셜센터 PT</t>
+          <t>짐플릭스 충장점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ssanglifegym@naver.com</t>
+          <t>gymflix@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1401-7847</t>
+          <t>0507-1355-2795</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주 서구 상무대로956번길 6 . 지하 1층</t>
+          <t>광주광역시 동구 구성로 147 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ssanglifegym</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1087,19 +1071,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w9iay88</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>264</v>
+        <v>85</v>
       </c>
       <c r="Q7" t="n">
-        <v>555</v>
+        <v>515</v>
       </c>
       <c r="R7" t="n">
-        <v>819</v>
+        <v>600</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1777617878</t>
+          <t>2007239115</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1777617878</t>
+          <t>https://m.place.naver.com/place/2007239115</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1143,39 +1123,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>짐플릭스 봉선점</t>
+          <t>달려라휘트니스 용봉점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gymflix@naver.com</t>
+          <t>randomize74@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1307-2795</t>
+          <t>0507-1440-7901</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주 남구 봉선로 205 4층 짐플릭스 봉선점</t>
+          <t>광주광역시 북구 용봉택지로 51 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://www.instagram.com/runfitness4_official</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1190,14 +1170,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wkfba0h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>217</v>
+        <v>538</v>
       </c>
       <c r="Q8" t="n">
-        <v>785</v>
+        <v>657</v>
       </c>
       <c r="R8" t="n">
-        <v>1002</v>
+        <v>1195</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1250527936</t>
+          <t>1849601273</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1250527936</t>
+          <t>https://m.place.naver.com/place/1849601273</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1241,35 +1217,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에스짐24시피트니스 진월점</t>
+          <t>짐플릭스 상무점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sgym3@naver.com</t>
+          <t>gymflix@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1448-9502</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 남구 서문대로 665 6층 SGYM 진월점</t>
+          <t>광주광역시 서구 상무연하로 48 7층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgym3/223208188125</t>
+          <t>https://www.gymflix.co.kr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1279,19 +1259,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4620r</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>413</v>
+        <v>53</v>
       </c>
       <c r="Q9" t="n">
-        <v>400</v>
+        <v>497</v>
       </c>
       <c r="R9" t="n">
-        <v>813</v>
+        <v>550</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1264832152</t>
+          <t>2060814649</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264832152</t>
+          <t>https://m.place.naver.com/place/2060814649</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1335,34 +1311,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>요가원</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>요가포레스트&amp;필라테스 봉선점</t>
+          <t>달려라휘트니스 첨단점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cheongdam_gwangju@naver.com</t>
+          <t>randomize74@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1392-4424</t>
+          <t>0507-1344-1192</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>광주 남구 봉선중앙로 51 3층 301-2호 요가포레스트</t>
+          <t>광주광역시 광산구 첨단중앙로106번길 65-7 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yogaforrest.pilates_bongseon?igsh=MWtyMXYwZnl1d2g0NA==</t>
+          <t>https://blog.naver.com/randomize74/224235673882</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,19 +1353,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4006k</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>26</v>
+        <v>434</v>
       </c>
       <c r="Q10" t="n">
-        <v>35</v>
+        <v>759</v>
       </c>
       <c r="R10" t="n">
-        <v>61</v>
+        <v>1193</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>38332243</t>
+          <t>1368410623</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38332243</t>
+          <t>https://m.place.naver.com/place/1368410623</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1433,34 +1405,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>봄필라테스</t>
+          <t>짐플릭스 운암점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bom_pila@naver.com</t>
+          <t>ayqyqu8a8@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1366-5608</t>
+          <t>0507-1414-0348</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>광주 서구 풍금로151번길 6-2 연수빌딩 5층</t>
+          <t>광주광역시 북구 서강로 67 황계빌딩 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_aYxjrn/chat</t>
+          <t>https://gymflix.co.kr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1480,17 +1452,13 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w04k3a0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1499,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>23</v>
+        <v>511</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>782</v>
       </c>
       <c r="R11" t="n">
-        <v>36</v>
+        <v>1293</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2028446140</t>
+          <t>38301225</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2028446140</t>
+          <t>https://m.place.naver.com/place/38301225</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1531,34 +1499,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
+          <t>짐플릭스 선운점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>allround_fitness5@naver.com</t>
+          <t>gymflix@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1438-7908</t>
+          <t>0507-1363-2795</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>광주 서구 운천로 23-1 2~3층</t>
+          <t>광주광역시 광산구 동곡로 739 7층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://allroundfitness.kr</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1573,22 +1541,18 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wkdxhjp</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1597,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>262</v>
+        <v>118</v>
       </c>
       <c r="Q12" t="n">
-        <v>620</v>
+        <v>700</v>
       </c>
       <c r="R12" t="n">
-        <v>882</v>
+        <v>818</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1612,12 +1576,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1709345373</t>
+          <t>1174990314</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709345373</t>
+          <t>https://m.place.naver.com/place/1174990314</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1629,39 +1593,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
+          <t>달려라휘트니스 상무지구점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>allround_fitness@naver.com</t>
+          <t>randomize74@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1461-2096</t>
+          <t>0507-1425-7906</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>광주 북구 북문대로 184 2층</t>
+          <t>광주광역시 서구 상무시민로 96 5층 달려라휘트니스 상무지구점</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_GRzxen/chat</t>
+          <t>https://www.instagram.com/runfitness3_official</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1676,17 +1640,13 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/we94hjj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1695,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>516</v>
+        <v>977</v>
       </c>
       <c r="Q13" t="n">
-        <v>285</v>
+        <v>1498</v>
       </c>
       <c r="R13" t="n">
-        <v>801</v>
+        <v>2475</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1710,15 +1670,763 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1509126970</t>
+          <t>1713507683</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509126970</t>
+          <t>https://m.place.naver.com/place/1713507683</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>24시 평생헬스 봉선주월점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cpp1234_@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1463-8264</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>광주광역시 남구 봉선로 50 1층, 2층</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/forlifegym_bongseon?igsh=cTMxN20wZHZsb2p5</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>195</v>
+      </c>
+      <c r="R14" t="n">
+        <v>317</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2047269084</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2047269084</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>레벨업피트니스 헬스&amp;PT 첨단점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>wjddbqls0383@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>광주광역시 광산구 첨단중앙로124번길 79 2층</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wjddbqls0383</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>732</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1076</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1808</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1078877238</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1078877238</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>달려라휘트니스 신세계농성점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>runfitness8@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1490-7905</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>광주광역시 서구 무진대로 956 5층</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/runfitness8_official/</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>295</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>61</v>
+      </c>
+      <c r="R16" t="n">
+        <v>356</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2012552358</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2012552358</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>평생헬스 매곡점 파나타공식센터</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>forlifegym_panatta@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1394-9938</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>광주광역시 북구 하백로29번길 38 라데사어반동 401호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/forlifegym_panatta</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>273</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>324</v>
+      </c>
+      <c r="R17" t="n">
+        <v>597</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1516267631</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1516267631</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>24시 평생헬스 수완장덕점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>suwanforlife@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1401-5896</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>광주광역시 광산구 왕버들로 57 3층</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_TWxdhG</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>502</v>
+      </c>
+      <c r="R18" t="n">
+        <v>776</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1167206594</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1167206594</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>24시 평생헬스 PT 선운지구점</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>blloodwang@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1318-5166</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>광주광역시 광산구 어등대로 418 5층 평생헬스</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/blloodwang</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>239</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>463</v>
+      </c>
+      <c r="R19" t="n">
+        <v>702</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1900183797</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1900183797</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>평생헬스 운남점 달팽이휘트니스</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>snailfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1336-4491</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>광주광역시 광산구 목련로153번길 79-1 5층 평생헬스 운남점 달팽이휘트니스</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_dVxdhG</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>349</v>
+      </c>
+      <c r="R20" t="n">
+        <v>559</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1769418943</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1769418943</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>액티브짐 수완점 헬스pt</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>zzangodeng@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1409-3600</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>광주광역시 광산구 임방울대로 330 10층 1001호, 1002호</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/active_gym3?igsh=cGM0eGx3M3JjdDBz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>170</v>
+      </c>
+      <c r="R21" t="n">
+        <v>283</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1986172577</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1986172577</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_health/광주_PT.xlsx
+++ b/naver-place-crawler/results_health/광주_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>짐플릭스 첨단점</t>
+          <t>에스짐문흥점 24시 헬스PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>gymflix@naver.com</t>
+          <t>sgym13@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1364-2795</t>
+          <t>0507-1369-6135</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>광주광역시 광산구 임방울대로800번길 72 3층</t>
+          <t>광주 북구 서하로 372 4층 SGYM 문흥점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://blog.naver.com/sgym13/223494722999</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,15 +601,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u0r4</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q2" t="n">
-        <v>885</v>
+        <v>119</v>
       </c>
       <c r="R2" t="n">
-        <v>1156</v>
+        <v>394</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,56 +640,56 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1955578541</t>
+          <t>1265291164</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1955578541</t>
+          <t>https://m.place.naver.com/place/1265291164</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24시 평생헬스 신창점</t>
+          <t>짐플릭스 첨단점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>aldusl7901@naver.com</t>
+          <t>gymflix@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1420-8259</t>
+          <t>0507-1364-2795</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>광주광역시 광산구 북문대로 431 1층</t>
+          <t>광주 광산구 임방울대로800번길 72 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forlifegym_shinchang/profilecard/?igsh=MTNyanVuZHVoaHNvcg==</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wkfba0h</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>477</v>
+        <v>274</v>
       </c>
       <c r="Q3" t="n">
-        <v>378</v>
+        <v>849</v>
       </c>
       <c r="R3" t="n">
-        <v>855</v>
+        <v>1123</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,24 +738,24 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1082086454</t>
+          <t>1955578541</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1082086454</t>
+          <t>https://m.place.naver.com/place/1955578541</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>광주광역시 광산구 임방울대로 342 8층</t>
+          <t>광주 광산구 임방울대로 342 8층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wkfba0h</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="Q4" t="n">
-        <v>749</v>
+        <v>724</v>
       </c>
       <c r="R4" t="n">
-        <v>1003</v>
+        <v>985</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,14 +846,14 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>광주광역시 서구 상무대로956번길 6 . 지하 1층</t>
+          <t>광주 서구 상무대로956번길 6 . 지하 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9iay88</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="Q5" t="n">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="R5" t="n">
-        <v>819</v>
+        <v>832</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -928,41 +944,41 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>짐플릭스 봉선점</t>
+          <t>짐플릭스 운암점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gymflix@naver.com</t>
+          <t>ayqyqu8a8@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1307-2795</t>
+          <t>0507-1414-0348</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>광주광역시 남구 봉선로 205 4층 짐플릭스 봉선점</t>
+          <t>광주 북구 서강로 67 황계빌딩 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://gymflix.co.kr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wkfba0h</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>217</v>
+        <v>519</v>
       </c>
       <c r="Q6" t="n">
-        <v>781</v>
+        <v>691</v>
       </c>
       <c r="R6" t="n">
-        <v>998</v>
+        <v>1210</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,29 +1032,29 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1250527936</t>
+          <t>38301225</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1250527936</t>
+          <t>https://m.place.naver.com/place/38301225</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>짐플릭스 충장점</t>
+          <t>짐플릭스 선운점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1045,13 +1065,13 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1355-2795</t>
+          <t>0507-1363-2795</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주광역시 동구 구성로 147 2층</t>
+          <t>광주 광산구 동곡로 739 7층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1076,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wkfba0h</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="Q7" t="n">
-        <v>515</v>
+        <v>659</v>
       </c>
       <c r="R7" t="n">
-        <v>600</v>
+        <v>777</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1130,47 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2007239115</t>
+          <t>1174990314</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2007239115</t>
+          <t>https://m.place.naver.com/place/1174990314</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>달려라휘트니스 용봉점</t>
+          <t>에스짐24시피트니스 진월점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>randomize74@naver.com</t>
+          <t>sgym3@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1440-7901</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주광역시 북구 용봉택지로 51 2층</t>
+          <t>광주 남구 서문대로 665 6층 SGYM 진월점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/runfitness4_official</t>
+          <t>https://blog.naver.com/sgym3/223208188125</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,15 +1185,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4620r</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>538</v>
+        <v>412</v>
       </c>
       <c r="Q8" t="n">
-        <v>657</v>
+        <v>401</v>
       </c>
       <c r="R8" t="n">
-        <v>1195</v>
+        <v>813</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1224,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1849601273</t>
+          <t>1264832152</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1849601273</t>
+          <t>https://m.place.naver.com/place/1264832152</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐플릭스 상무점</t>
+          <t>봄필라테스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gymflix@naver.com</t>
+          <t>bom_pila@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1448-9502</t>
+          <t>0507-1366-5608</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주광역시 서구 상무연하로 48 7층</t>
+          <t>광주 서구 풍금로151번길 6-2 연수빌딩 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr</t>
+          <t>http://pf.kakao.com/_aYxjrn/chat</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1264,13 +1288,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w04k3a0</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1279,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="Q9" t="n">
-        <v>497</v>
+        <v>13</v>
       </c>
       <c r="R9" t="n">
-        <v>550</v>
+        <v>36</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,56 +1322,56 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2060814649</t>
+          <t>2028446140</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2060814649</t>
+          <t>https://m.place.naver.com/place/2028446140</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>달려라휘트니스 첨단점</t>
+          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>randomize74@naver.com</t>
+          <t>allround_fitness5@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1344-1192</t>
+          <t>0507-1438-7908</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>광주광역시 광산구 첨단중앙로106번길 65-7 2층</t>
+          <t>광주 서구 운천로 23-1 2~3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/randomize74/224235673882</t>
+          <t>https://allroundfitness.kr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1358,13 +1386,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wkdxhjp</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1373,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>434</v>
+        <v>266</v>
       </c>
       <c r="Q10" t="n">
-        <v>759</v>
+        <v>636</v>
       </c>
       <c r="R10" t="n">
-        <v>1193</v>
+        <v>902</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1420,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1368410623</t>
+          <t>1709345373</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1368410623</t>
+          <t>https://m.place.naver.com/place/1709345373</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐플릭스 운암점</t>
+          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ayqyqu8a8@naver.com</t>
+          <t>allround_fitness@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1414-0348</t>
+          <t>0507-1461-2096</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>광주광역시 북구 서강로 67 황계빌딩 4층</t>
+          <t>광주 북구 북문대로 184 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://gymflix.co.kr</t>
+          <t>http://pf.kakao.com/_GRzxen/chat</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1452,13 +1484,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/we94hjj</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1467,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="Q11" t="n">
-        <v>782</v>
+        <v>291</v>
       </c>
       <c r="R11" t="n">
-        <v>1293</v>
+        <v>811</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,56 +1518,56 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>38301225</t>
+          <t>1509126970</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38301225</t>
+          <t>https://m.place.naver.com/place/1509126970</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>짐플릭스 선운점</t>
+          <t>요가포레스트&amp;필라테스 상무점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>gymflix@naver.com</t>
+          <t>cheongdam_gwangju@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1363-2795</t>
+          <t>0507-1300-0724</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>광주광역시 광산구 동곡로 739 7층</t>
+          <t>광주 서구 상무중앙로 70 4층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://www.instagram.com/yogaforrest.pilates_sangmu?igsh=MWVxeDl2bGhhZnZrcQ==</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1546,10 +1582,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4006k</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1561,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="Q12" t="n">
-        <v>700</v>
+        <v>105</v>
       </c>
       <c r="R12" t="n">
-        <v>818</v>
+        <v>153</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,859 +1616,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1174990314</t>
+          <t>1326715625</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174990314</t>
+          <t>https://m.place.naver.com/place/1326715625</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>달려라휘트니스 상무지구점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>randomize74@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1425-7906</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>광주광역시 서구 상무시민로 96 5층 달려라휘트니스 상무지구점</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/runfitness3_official</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>977</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1498</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2475</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1713507683</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1713507683</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>24시 평생헬스 봉선주월점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>cpp1234_@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1463-8264</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>광주광역시 남구 봉선로 50 1층, 2층</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/forlifegym_bongseon?igsh=cTMxN20wZHZsb2p5</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>122</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>195</v>
-      </c>
-      <c r="R14" t="n">
-        <v>317</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2047269084</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2047269084</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>레벨업피트니스 헬스&amp;PT 첨단점</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>wjddbqls0383@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>광주광역시 광산구 첨단중앙로124번길 79 2층</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/wjddbqls0383</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>732</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1076</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1808</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1078877238</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1078877238</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>달려라휘트니스 신세계농성점</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>runfitness8@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1490-7905</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>광주광역시 서구 무진대로 956 5층</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/runfitness8_official/</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>295</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>61</v>
-      </c>
-      <c r="R16" t="n">
-        <v>356</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2012552358</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2012552358</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>평생헬스 매곡점 파나타공식센터</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>forlifegym_panatta@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1394-9938</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>광주광역시 북구 하백로29번길 38 라데사어반동 401호</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/forlifegym_panatta</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>273</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>324</v>
-      </c>
-      <c r="R17" t="n">
-        <v>597</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1516267631</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1516267631</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>24시 평생헬스 수완장덕점</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>suwanforlife@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1401-5896</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>광주광역시 광산구 왕버들로 57 3층</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>http://pf.kakao.com/_TWxdhG</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>274</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>502</v>
-      </c>
-      <c r="R18" t="n">
-        <v>776</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1167206594</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1167206594</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>24시 평생헬스 PT 선운지구점</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>blloodwang@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1318-5166</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>광주광역시 광산구 어등대로 418 5층 평생헬스</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/blloodwang</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>239</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>463</v>
-      </c>
-      <c r="R19" t="n">
-        <v>702</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1900183797</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1900183797</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>평생헬스 운남점 달팽이휘트니스</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>snailfitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1336-4491</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>광주광역시 광산구 목련로153번길 79-1 5층 평생헬스 운남점 달팽이휘트니스</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>http://pf.kakao.com/_dVxdhG</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>210</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>349</v>
-      </c>
-      <c r="R20" t="n">
-        <v>559</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1769418943</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1769418943</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>액티브짐 수완점 헬스pt</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>zzangodeng@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1409-3600</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>광주광역시 광산구 임방울대로 330 10층 1001호, 1002호</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/active_gym3?igsh=cGM0eGx3M3JjdDBz</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>113</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>170</v>
-      </c>
-      <c r="R21" t="n">
-        <v>283</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1986172577</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1986172577</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/광주_PT.xlsx
+++ b/naver-place-crawler/results_health/광주_PT.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -726,10 +726,10 @@
         <v>274</v>
       </c>
       <c r="Q3" t="n">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="R3" t="n">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q4" t="n">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="R4" t="n">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q5" t="n">
         <v>559</v>
       </c>
       <c r="R5" t="n">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="Q6" t="n">
         <v>691</v>
       </c>
       <c r="R6" t="n">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1054,34 +1054,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>짐플릭스 선운점</t>
+          <t>달려라휘트니스 신세계농성점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gymflix@naver.com</t>
+          <t>runfitness8@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1363-2795</t>
+          <t>0507-1490-7905</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주 광산구 동곡로 739 7층</t>
+          <t>광주 서구 무진대로 956 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://www.instagram.com/runfitness8_official/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wkfba0h</t>
+          <t>https://talk.naver.com/ct/wjg3nyo</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>118</v>
+        <v>331</v>
       </c>
       <c r="Q7" t="n">
-        <v>659</v>
+        <v>74</v>
       </c>
       <c r="R7" t="n">
-        <v>777</v>
+        <v>405</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1174990314</t>
+          <t>2012552358</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174990314</t>
+          <t>https://m.place.naver.com/place/2012552358</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1212,10 +1212,10 @@
         <v>412</v>
       </c>
       <c r="Q8" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="R8" t="n">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1344,34 +1344,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
+          <t>24시 헬스 PT 제로백피트니스 첨단점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>allround_fitness5@naver.com</t>
+          <t>zeroback2022@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1438-7908</t>
+          <t>0507-1338-8873</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>광주 서구 운천로 23-1 2~3층</t>
+          <t>광주 광산구 첨단중앙로106번길 29 5층 제로백피트니스</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://allroundfitness.kr</t>
+          <t>https://blog.naver.com/zeroback2022/223794553588</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1391,12 +1391,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wkdxhjp</t>
+          <t>https://talk.naver.com/ct/w5ycoi</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>266</v>
+        <v>628</v>
       </c>
       <c r="Q10" t="n">
-        <v>636</v>
+        <v>1040</v>
       </c>
       <c r="R10" t="n">
-        <v>902</v>
+        <v>1668</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1709345373</t>
+          <t>1862122664</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709345373</t>
+          <t>https://m.place.naver.com/place/1862122664</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1442,29 +1442,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
+          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>allround_fitness@naver.com</t>
+          <t>allround_fitness5@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1461-2096</t>
+          <t>0507-1438-7908</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>광주 북구 북문대로 184 2층</t>
+          <t>광주 서구 운천로 23-1 2~3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_GRzxen/chat</t>
+          <t>https://allroundfitness.kr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/we94hjj</t>
+          <t>https://talk.naver.com/ct/wkdxhjp</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>520</v>
+        <v>266</v>
       </c>
       <c r="Q11" t="n">
-        <v>291</v>
+        <v>636</v>
       </c>
       <c r="R11" t="n">
-        <v>811</v>
+        <v>902</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,56 +1518,56 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1509126970</t>
+          <t>1709345373</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509126970</t>
+          <t>https://m.place.naver.com/place/1709345373</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>요가포레스트&amp;필라테스 상무점</t>
+          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>cheongdam_gwangju@naver.com</t>
+          <t>allround_fitness@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1300-0724</t>
+          <t>0507-1461-2096</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>광주 서구 상무중앙로 70 4층</t>
+          <t>광주 북구 북문대로 184 2층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yogaforrest.pilates_sangmu?igsh=MWVxeDl2bGhhZnZrcQ==</t>
+          <t>http://pf.kakao.com/_GRzxen/chat</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4006k</t>
+          <t>https://talk.naver.com/ct/we94hjj</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>48</v>
+        <v>520</v>
       </c>
       <c r="Q12" t="n">
-        <v>105</v>
+        <v>291</v>
       </c>
       <c r="R12" t="n">
-        <v>153</v>
+        <v>811</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1616,17 +1616,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1326715625</t>
+          <t>1509126970</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1326715625</t>
+          <t>https://m.place.naver.com/place/1509126970</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/광주_PT.xlsx
+++ b/naver-place-crawler/results_health/광주_PT.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24시 헬스 PT 제로백피트니스 첨단점</t>
+          <t>24시 헬스 PT 제로백피트니스 상무지구점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1355,18 +1355,18 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1338-8873</t>
+          <t>0507-1490-0243</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>광주 광산구 첨단중앙로106번길 29 5층 제로백피트니스</t>
+          <t>광주 서구 상무중앙로 7 8층 802호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223794553588</t>
+          <t>https://blog.naver.com/zeroback2022/223830063211</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ycoi</t>
+          <t>https://talk.naver.com/ct/w5yb72</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>628</v>
+        <v>317</v>
       </c>
       <c r="Q10" t="n">
-        <v>1040</v>
+        <v>612</v>
       </c>
       <c r="R10" t="n">
-        <v>1668</v>
+        <v>929</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1862122664</t>
+          <t>1013874419</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1862122664</t>
+          <t>https://m.place.naver.com/place/1013874419</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1442,34 +1442,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
+          <t>24시 헬스 PT 제로백피트니스 첨단점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>allround_fitness5@naver.com</t>
+          <t>zeroback2022@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1438-7908</t>
+          <t>0507-1338-8873</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>광주 서구 운천로 23-1 2~3층</t>
+          <t>광주 광산구 첨단중앙로106번길 29 5층 제로백피트니스</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://allroundfitness.kr</t>
+          <t>https://blog.naver.com/zeroback2022/223794553588</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wkdxhjp</t>
+          <t>https://talk.naver.com/ct/w5ycoi</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>266</v>
+        <v>628</v>
       </c>
       <c r="Q11" t="n">
-        <v>636</v>
+        <v>1040</v>
       </c>
       <c r="R11" t="n">
-        <v>902</v>
+        <v>1668</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1709345373</t>
+          <t>1862122664</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709345373</t>
+          <t>https://m.place.naver.com/place/1862122664</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1540,29 +1540,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
+          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>allround_fitness@naver.com</t>
+          <t>allround_fitness5@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1461-2096</t>
+          <t>0507-1438-7908</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>광주 북구 북문대로 184 2층</t>
+          <t>광주 서구 운천로 23-1 2~3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_GRzxen/chat</t>
+          <t>https://allroundfitness.kr</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/we94hjj</t>
+          <t>https://talk.naver.com/ct/wkdxhjp</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>520</v>
+        <v>266</v>
       </c>
       <c r="Q12" t="n">
-        <v>291</v>
+        <v>636</v>
       </c>
       <c r="R12" t="n">
-        <v>811</v>
+        <v>902</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1509126970</t>
+          <t>1709345373</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509126970</t>
+          <t>https://m.place.naver.com/place/1709345373</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/광주_PT.xlsx
+++ b/naver-place-crawler/results_health/광주_PT.xlsx
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -662,7 +662,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>짐플릭스 첨단점</t>
+          <t>짐플릭스 수완점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -673,13 +673,13 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1364-2795</t>
+          <t>0507-1383-2795</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>광주 광산구 임방울대로800번길 72 3층</t>
+          <t>광주 광산구 임방울대로 342 8층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="Q3" t="n">
-        <v>850</v>
+        <v>726</v>
       </c>
       <c r="R3" t="n">
-        <v>1124</v>
+        <v>988</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1955578541</t>
+          <t>1999324427</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1955578541</t>
+          <t>https://m.place.naver.com/place/1999324427</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>짐플릭스 수완점</t>
+          <t>짐플릭스 첨단점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -771,13 +771,13 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1383-2795</t>
+          <t>0507-1364-2795</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>광주 광산구 임방울대로 342 8층</t>
+          <t>광주 광산구 임방울대로800번길 72 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="Q4" t="n">
-        <v>726</v>
+        <v>850</v>
       </c>
       <c r="R4" t="n">
-        <v>988</v>
+        <v>1124</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1999324427</t>
+          <t>1955578541</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1999324427</t>
+          <t>https://m.place.naver.com/place/1955578541</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q5" t="n">
         <v>559</v>
       </c>
       <c r="R5" t="n">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1054,34 +1054,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>달려라휘트니스 신세계농성점</t>
+          <t>짐플릭스 봉선점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>runfitness8@naver.com</t>
+          <t>gymflix@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1490-7905</t>
+          <t>0507-1307-2795</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주 서구 무진대로 956 5층</t>
+          <t>광주 남구 봉선로 205 4층 짐플릭스 봉선점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/runfitness8_official/</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wjg3nyo</t>
+          <t>https://talk.naver.com/ct/wkfba0h</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>331</v>
+        <v>217</v>
       </c>
       <c r="Q7" t="n">
-        <v>74</v>
+        <v>752</v>
       </c>
       <c r="R7" t="n">
-        <v>405</v>
+        <v>969</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2012552358</t>
+          <t>1250527936</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2012552358</t>
+          <t>https://m.place.naver.com/place/1250527936</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1147,35 +1147,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에스짐24시피트니스 진월점</t>
+          <t>봄필라테스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sgym3@naver.com</t>
+          <t>bom_pila@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1366-5608</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주 남구 서문대로 665 6층 SGYM 진월점</t>
+          <t>광주 서구 풍금로151번길 6-2 연수빌딩 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgym3/223208188125</t>
+          <t>http://pf.kakao.com/_aYxjrn/chat</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1185,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1195,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4620r</t>
+          <t>https://talk.naver.com/ct/w04k3a0</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>412</v>
+        <v>23</v>
       </c>
       <c r="Q8" t="n">
-        <v>402</v>
+        <v>13</v>
       </c>
       <c r="R8" t="n">
-        <v>814</v>
+        <v>36</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1264832152</t>
+          <t>2028446140</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264832152</t>
+          <t>https://m.place.naver.com/place/2028446140</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1241,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>봄필라테스</t>
+          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bom_pila@naver.com</t>
+          <t>allround_fitness5@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1366-5608</t>
+          <t>0507-1438-7908</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 서구 풍금로151번길 6-2 연수빌딩 5층</t>
+          <t>광주 서구 운천로 23-1 2~3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_aYxjrn/chat</t>
+          <t>https://allroundfitness.kr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1293,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w04k3a0</t>
+          <t>https://talk.naver.com/ct/wkdxhjp</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>23</v>
+        <v>266</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>636</v>
       </c>
       <c r="R9" t="n">
-        <v>36</v>
+        <v>902</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2028446140</t>
+          <t>1709345373</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2028446140</t>
+          <t>https://m.place.naver.com/place/1709345373</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1344,34 +1348,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24시 헬스 PT 제로백피트니스 상무지구점</t>
+          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>zeroback2022@naver.com</t>
+          <t>allround_fitness@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1490-0243</t>
+          <t>0507-1461-2096</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>광주 서구 상무중앙로 7 8층 802호</t>
+          <t>광주 북구 북문대로 184 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223830063211</t>
+          <t>http://pf.kakao.com/_GRzxen/chat</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1381,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,27 +1395,27 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5yb72</t>
+          <t>https://talk.naver.com/ct/we94hjj</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>317</v>
+        <v>520</v>
       </c>
       <c r="Q10" t="n">
-        <v>612</v>
+        <v>291</v>
       </c>
       <c r="R10" t="n">
-        <v>929</v>
+        <v>811</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1013874419</t>
+          <t>1509126970</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013874419</t>
+          <t>https://m.place.naver.com/place/1509126970</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1442,29 +1446,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24시 헬스 PT 제로백피트니스 첨단점</t>
+          <t>천하의벽포짐 헬스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>zeroback2022@naver.com</t>
+          <t>ymj0496@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1338-8873</t>
+          <t>0507-1408-6671</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>광주 광산구 첨단중앙로106번길 29 5층 제로백피트니스</t>
+          <t>광주 서구 운천로 65 상가2층 천하의벽포짐</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223794553588</t>
+          <t>https://blog.naver.com/ymj0496</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1489,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ycoi</t>
+          <t>https://talk.naver.com/ct/w42ixh</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>628</v>
+        <v>52</v>
       </c>
       <c r="Q11" t="n">
-        <v>1040</v>
+        <v>14</v>
       </c>
       <c r="R11" t="n">
-        <v>1668</v>
+        <v>66</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1862122664</t>
+          <t>1564896495</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1862122664</t>
+          <t>https://m.place.naver.com/place/1564896495</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1540,34 +1544,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
+          <t>나우휘트니스 헬스&amp;PT 봉선점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>allround_fitness5@naver.com</t>
+          <t>nowfitness_1@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1438-7908</t>
+          <t>0507-1487-8892</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>광주 서구 운천로 23-1 2~3층</t>
+          <t>광주 남구 봉선2로 41 스카이빌딩 3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://allroundfitness.kr</t>
+          <t>https://blog.naver.com/nowfitness_1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1587,12 +1591,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wkdxhjp</t>
+          <t>https://talk.naver.com/ct/w41axl</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1601,13 +1605,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>266</v>
+        <v>517</v>
       </c>
       <c r="Q12" t="n">
-        <v>636</v>
+        <v>252</v>
       </c>
       <c r="R12" t="n">
-        <v>902</v>
+        <v>769</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1616,12 +1620,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1709345373</t>
+          <t>1006368175</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709345373</t>
+          <t>https://m.place.naver.com/place/1006368175</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/광주_PT.xlsx
+++ b/naver-place-crawler/results_health/광주_PT.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
+          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>allround_fitness5@naver.com</t>
+          <t>allround_fitness@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1438-7908</t>
+          <t>0507-1461-2096</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 서구 운천로 23-1 2~3층</t>
+          <t>광주 북구 북문대로 184 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://allroundfitness.kr</t>
+          <t>http://pf.kakao.com/_GRzxen/chat</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wkdxhjp</t>
+          <t>https://talk.naver.com/ct/we94hjj</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>266</v>
+        <v>520</v>
       </c>
       <c r="Q9" t="n">
-        <v>636</v>
+        <v>291</v>
       </c>
       <c r="R9" t="n">
-        <v>902</v>
+        <v>811</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1709345373</t>
+          <t>1509126970</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709345373</t>
+          <t>https://m.place.naver.com/place/1509126970</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,39 +1343,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
+          <t>레벨업피트니스 헬스&amp;PT 첨단점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>allround_fitness@naver.com</t>
+          <t>wjddbqls0383@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1461-2096</t>
+          <t>0507-1317-9336</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>광주 북구 북문대로 184 2층</t>
+          <t>광주 광산구 첨단중앙로124번길 79 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_GRzxen/chat</t>
+          <t>https://blog.naver.com/wjddbqls0383</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1385,22 +1385,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/we94hjj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1409,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>520</v>
+        <v>745</v>
       </c>
       <c r="Q10" t="n">
-        <v>291</v>
+        <v>1081</v>
       </c>
       <c r="R10" t="n">
-        <v>811</v>
+        <v>1826</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1509126970</t>
+          <t>1078877238</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509126970</t>
+          <t>https://m.place.naver.com/place/1078877238</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/광주_PT.xlsx
+++ b/naver-place-crawler/results_health/광주_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>광주 북구 서하로 372 4층 SGYM 문흥점</t>
+          <t>광주광역시 북구 서하로 372 4층 SGYM 문흥점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5u0r4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>광주 광산구 임방울대로 342 8층</t>
+          <t>광주광역시 광산구 임방울대로 342 8층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wkfba0h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -777,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>광주 광산구 임방울대로800번길 72 3층</t>
+          <t>광주광역시 광산구 임방울대로800번길 72 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wkfba0h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -875,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>광주 서구 상무대로956번길 6 . 지하 1층</t>
+          <t>광주광역시 서구 상무대로956번길 6 . 지하 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w9iay88</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -973,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>광주 북구 서강로 67 황계빌딩 4층</t>
+          <t>광주광역시 북구 서강로 67 황계빌딩 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wkfba0h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1071,7 +1051,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주 남구 봉선로 205 4층 짐플릭스 봉선점</t>
+          <t>광주광역시 남구 봉선로 205 4층 짐플릭스 봉선점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1096,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wkfba0h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1165,7 +1141,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주 남구 서문대로 665 6층 SGYM 진월점</t>
+          <t>광주광역시 남구 서문대로 665 6층 SGYM 진월점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1190,14 +1166,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4620r</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1212,10 +1184,10 @@
         <v>411</v>
       </c>
       <c r="Q8" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="R8" t="n">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1263,7 +1235,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 서구 마륵복개로 91</t>
+          <t>광주광역시 서구 마륵복개로 91</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1288,14 +1260,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4tqh8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1442,34 +1410,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
+          <t>24시 헬스 PT 제로백피트니스 첨단점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>allround_fitness5@naver.com</t>
+          <t>zeroback2022@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1438-7908</t>
+          <t>0507-1338-8873</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>광주 서구 운천로 23-1 2~3층</t>
+          <t>광주광역시 광산구 첨단중앙로106번길 29 5층 제로백피트니스</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://allroundfitness.kr</t>
+          <t>https://blog.naver.com/zeroback2022/223794553588</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1484,17 +1452,13 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wkdxhjp</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1503,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>266</v>
+        <v>628</v>
       </c>
       <c r="Q11" t="n">
-        <v>636</v>
+        <v>1042</v>
       </c>
       <c r="R11" t="n">
-        <v>902</v>
+        <v>1670</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,113 +1482,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1709345373</t>
+          <t>1862122664</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709345373</t>
+          <t>https://m.place.naver.com/place/1862122664</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>allround_fitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1461-2096</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>광주 북구 북문대로 184 2층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>http://pf.kakao.com/_GRzxen/chat</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/we94hjj</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>520</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>291</v>
-      </c>
-      <c r="R12" t="n">
-        <v>811</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1509126970</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1509126970</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/광주_PT.xlsx
+++ b/naver-place-crawler/results_health/광주_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>광주광역시 북구 서하로 372 4층 SGYM 문흥점</t>
+          <t>광주 북구 서하로 372 4층 SGYM 문흥점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u0r4</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -646,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>광주광역시 광산구 임방울대로 342 8층</t>
+          <t>광주 광산구 임방울대로 342 8층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wkfba0h</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -740,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>광주광역시 광산구 임방울대로800번길 72 3층</t>
+          <t>광주 광산구 임방울대로800번길 72 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wkfba0h</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -834,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>광주광역시 서구 상무대로956번길 6 . 지하 1층</t>
+          <t>광주 서구 상무대로956번길 6 . 지하 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9iay88</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -928,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -957,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>광주광역시 북구 서강로 67 황계빌딩 4층</t>
+          <t>광주 북구 서강로 67 황계빌딩 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wkfba0h</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="Q6" t="n">
         <v>691</v>
       </c>
       <c r="R6" t="n">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1022,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1071,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주광역시 남구 봉선로 205 4층 짐플릭스 봉선점</t>
+          <t>광주 남구 봉선로 205 4층 짐플릭스 봉선점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1076,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wkfba0h</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1116,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1128,25 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에스짐24시피트니스 진월점</t>
+          <t>WE휘트니스 헬스 PT 필라테스 상무점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sgym3@naver.com</t>
+          <t>we_fitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1388-6900</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주광역시 남구 서문대로 665 6층 SGYM 진월점</t>
+          <t>광주 서구 마륵복개로 91</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgym3/223208188125</t>
+          <t>https://www.instagram.com/_wefit_sangmu/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1161,15 +1189,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4tqh8</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1181,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>411</v>
+        <v>301</v>
       </c>
       <c r="Q8" t="n">
-        <v>401</v>
+        <v>835</v>
       </c>
       <c r="R8" t="n">
-        <v>812</v>
+        <v>1136</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,56 +1228,56 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1264832152</t>
+          <t>36670044</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264832152</t>
+          <t>https://m.place.naver.com/place/36670044</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WE휘트니스 헬스 PT 필라테스 상무점</t>
+          <t>봄필라테스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>we_fitness@naver.com</t>
+          <t>bom_pila@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1388-6900</t>
+          <t>0507-1366-5608</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주광역시 서구 마륵복개로 91</t>
+          <t>광주 서구 풍금로151번길 6-2 연수빌딩 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_wefit_sangmu/</t>
+          <t>http://pf.kakao.com/_aYxjrn/chat</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1260,13 +1292,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w04k3a0</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1275,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>301</v>
+        <v>23</v>
       </c>
       <c r="Q9" t="n">
-        <v>835</v>
+        <v>13</v>
       </c>
       <c r="R9" t="n">
-        <v>1136</v>
+        <v>36</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,51 +1326,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>36670044</t>
+          <t>2028446140</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36670044</t>
+          <t>https://m.place.naver.com/place/2028446140</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>봄필라테스</t>
+          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bom_pila@naver.com</t>
+          <t>allround_fitness5@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1366-5608</t>
+          <t>0507-1438-7908</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>광주 서구 풍금로151번길 6-2 연수빌딩 5층</t>
+          <t>광주 서구 운천로 23-1 2~3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_aYxjrn/chat</t>
+          <t>https://allroundfitness.kr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1349,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1359,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w04k3a0</t>
+          <t>https://talk.naver.com/ct/wkdxhjp</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1373,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>23</v>
+        <v>267</v>
       </c>
       <c r="Q10" t="n">
-        <v>13</v>
+        <v>637</v>
       </c>
       <c r="R10" t="n">
-        <v>36</v>
+        <v>904</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2028446140</t>
+          <t>1709345373</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2028446140</t>
+          <t>https://m.place.naver.com/place/1709345373</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1410,34 +1446,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24시 헬스 PT 제로백피트니스 첨단점</t>
+          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>zeroback2022@naver.com</t>
+          <t>allround_fitness@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1338-8873</t>
+          <t>0507-1461-2096</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>광주광역시 광산구 첨단중앙로106번길 29 5층 제로백피트니스</t>
+          <t>광주 북구 북문대로 184 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223794553588</t>
+          <t>http://pf.kakao.com/_GRzxen/chat</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1447,18 +1483,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/we94hjj</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1467,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>628</v>
+        <v>520</v>
       </c>
       <c r="Q11" t="n">
-        <v>1042</v>
+        <v>291</v>
       </c>
       <c r="R11" t="n">
-        <v>1670</v>
+        <v>811</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1522,111 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1862122664</t>
+          <t>1509126970</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1862122664</t>
+          <t>https://m.place.naver.com/place/1509126970</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>레벨업피트니스 헬스&amp;PT 첨단점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>wjddbqls0383@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1317-9336</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>광주 광산구 첨단중앙로124번길 79 2층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wjddbqls0383</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>747</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1081</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1828</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1078877238</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1078877238</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/광주_PT.xlsx
+++ b/naver-place-crawler/results_health/광주_PT.xlsx
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -628,10 +628,10 @@
         <v>275</v>
       </c>
       <c r="Q2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="R2" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         <v>262</v>
       </c>
       <c r="Q3" t="n">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="R3" t="n">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q4" t="n">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="R4" t="n">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q5" t="n">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="R5" t="n">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>짐플릭스 운암점</t>
+          <t>짐플릭스 봉선점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ayqyqu8a8@naver.com</t>
+          <t>gymflix@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1414-0348</t>
+          <t>0507-1307-2795</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>광주 북구 서강로 67 황계빌딩 4층</t>
+          <t>광주 남구 봉선로 205 4층 짐플릭스 봉선점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://gymflix.co.kr</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>519</v>
+        <v>217</v>
       </c>
       <c r="Q6" t="n">
-        <v>691</v>
+        <v>750</v>
       </c>
       <c r="R6" t="n">
-        <v>1210</v>
+        <v>967</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>38301225</t>
+          <t>1250527936</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38301225</t>
+          <t>https://m.place.naver.com/place/1250527936</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>짐플릭스 봉선점</t>
+          <t>짐플릭스 선운점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1065,13 +1065,13 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1307-2795</t>
+          <t>0507-1363-2795</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주 남구 봉선로 205 4층 짐플릭스 봉선점</t>
+          <t>광주 광산구 동곡로 739 7층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>217</v>
+        <v>118</v>
       </c>
       <c r="Q7" t="n">
-        <v>752</v>
+        <v>657</v>
       </c>
       <c r="R7" t="n">
-        <v>969</v>
+        <v>775</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1250527936</t>
+          <t>1174990314</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1250527936</t>
+          <t>https://m.place.naver.com/place/1174990314</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,29 +1152,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WE휘트니스 헬스 PT 필라테스 상무점</t>
+          <t>에스짐24시피트니스 진월점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>we_fitness@naver.com</t>
+          <t>sgym3@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1388-6900</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주 서구 마륵복개로 91</t>
+          <t>광주 남구 서문대로 665 6층 SGYM 진월점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_wefit_sangmu/</t>
+          <t>https://blog.naver.com/sgym3/223208188125</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4tqh8</t>
+          <t>https://talk.naver.com/ct/w4620r</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>301</v>
+        <v>411</v>
       </c>
       <c r="Q8" t="n">
-        <v>835</v>
+        <v>401</v>
       </c>
       <c r="R8" t="n">
-        <v>1136</v>
+        <v>812</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>36670044</t>
+          <t>1264832152</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36670044</t>
+          <t>https://m.place.naver.com/place/1264832152</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1245,39 +1241,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>봄필라테스</t>
+          <t>WE휘트니스 헬스 PT 필라테스 상무점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bom_pila@naver.com</t>
+          <t>we_fitness@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1366-5608</t>
+          <t>0507-1388-6900</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 서구 풍금로151번길 6-2 연수빌딩 5층</t>
+          <t>광주 서구 마륵복개로 91</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_aYxjrn/chat</t>
+          <t>https://www.instagram.com/_wefit_sangmu/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1297,12 +1293,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w04k3a0</t>
+          <t>https://talk.naver.com/ct/w4tqh8</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>23</v>
+        <v>302</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>835</v>
       </c>
       <c r="R9" t="n">
-        <v>36</v>
+        <v>1137</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2028446140</t>
+          <t>36670044</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2028446140</t>
+          <t>https://m.place.naver.com/place/36670044</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,39 +1339,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>요가원</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
+          <t>요가포레스트&amp;필라테스 봉선점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>allround_fitness5@naver.com</t>
+          <t>cheongdam_gwangju@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1438-7908</t>
+          <t>0507-1392-4424</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>광주 서구 운천로 23-1 2~3층</t>
+          <t>광주 남구 봉선중앙로 51 3층 301-2호 요가포레스트</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://allroundfitness.kr</t>
+          <t>https://www.instagram.com/yogaforrest.pilates_bongseon?igsh=MWtyMXYwZnl1d2g0NA==</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1385,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,12 +1391,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wkdxhjp</t>
+          <t>https://talk.naver.com/ct/w4006k</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1409,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>267</v>
+        <v>26</v>
       </c>
       <c r="Q10" t="n">
-        <v>637</v>
+        <v>35</v>
       </c>
       <c r="R10" t="n">
-        <v>904</v>
+        <v>61</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1709345373</t>
+          <t>38332243</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709345373</t>
+          <t>https://m.place.naver.com/place/38332243</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1441,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
+          <t>봄필라테스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>allround_fitness@naver.com</t>
+          <t>bom_pila@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1461-2096</t>
+          <t>0507-1366-5608</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>광주 북구 북문대로 184 2층</t>
+          <t>광주 서구 풍금로151번길 6-2 연수빌딩 5층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_GRzxen/chat</t>
+          <t>http://pf.kakao.com/_aYxjrn/chat</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1493,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/we94hjj</t>
+          <t>https://talk.naver.com/ct/w04k3a0</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>520</v>
+        <v>23</v>
       </c>
       <c r="Q11" t="n">
-        <v>291</v>
+        <v>13</v>
       </c>
       <c r="R11" t="n">
-        <v>811</v>
+        <v>36</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1509126970</t>
+          <t>2028446140</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509126970</t>
+          <t>https://m.place.naver.com/place/2028446140</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1539,34 +1535,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>레벨업피트니스 헬스&amp;PT 첨단점</t>
+          <t>24시 헬스 PT 제로백피트니스 상무지구점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>wjddbqls0383@naver.com</t>
+          <t>zeroback2022@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1317-9336</t>
+          <t>0507-1490-0243</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>광주 광산구 첨단중앙로124번길 79 2층</t>
+          <t>광주 서구 상무중앙로 7 8층 802호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wjddbqls0383</t>
+          <t>https://blog.naver.com/zeroback2022/223830063211</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1586,10 +1582,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yb72</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1597,17 +1597,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>747</v>
+        <v>316</v>
       </c>
       <c r="Q12" t="n">
-        <v>1081</v>
+        <v>614</v>
       </c>
       <c r="R12" t="n">
-        <v>1828</v>
+        <v>930</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1078877238</t>
+          <t>1013874419</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1078877238</t>
+          <t>https://m.place.naver.com/place/1013874419</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/광주_PT.xlsx
+++ b/naver-place-crawler/results_health/광주_PT.xlsx
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1152,25 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에스짐24시피트니스 진월점</t>
+          <t>WE휘트니스 헬스 PT 필라테스 상무점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sgym3@naver.com</t>
+          <t>we_fitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1388-6900</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주 남구 서문대로 665 6층 SGYM 진월점</t>
+          <t>광주 서구 마륵복개로 91</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgym3/223208188125</t>
+          <t>https://www.instagram.com/_wefit_sangmu/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1195,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4620r</t>
+          <t>https://talk.naver.com/ct/w4tqh8</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>411</v>
+        <v>302</v>
       </c>
       <c r="Q8" t="n">
-        <v>401</v>
+        <v>835</v>
       </c>
       <c r="R8" t="n">
-        <v>812</v>
+        <v>1137</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,56 +1228,56 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1264832152</t>
+          <t>36670044</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264832152</t>
+          <t>https://m.place.naver.com/place/36670044</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WE휘트니스 헬스 PT 필라테스 상무점</t>
+          <t>봄필라테스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>we_fitness@naver.com</t>
+          <t>bom_pila@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1388-6900</t>
+          <t>0507-1366-5608</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 서구 마륵복개로 91</t>
+          <t>광주 서구 풍금로151번길 6-2 연수빌딩 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_wefit_sangmu/</t>
+          <t>http://pf.kakao.com/_aYxjrn/chat</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1293,12 +1297,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4tqh8</t>
+          <t>https://talk.naver.com/ct/w04k3a0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1307,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>302</v>
+        <v>23</v>
       </c>
       <c r="Q9" t="n">
-        <v>835</v>
+        <v>13</v>
       </c>
       <c r="R9" t="n">
-        <v>1137</v>
+        <v>36</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,56 +1326,56 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>36670044</t>
+          <t>2028446140</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36670044</t>
+          <t>https://m.place.naver.com/place/2028446140</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>요가원</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>요가포레스트&amp;필라테스 봉선점</t>
+          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cheongdam_gwangju@naver.com</t>
+          <t>allround_fitness5@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1392-4424</t>
+          <t>0507-1438-7908</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>광주 남구 봉선중앙로 51 3층 301-2호 요가포레스트</t>
+          <t>광주 서구 운천로 23-1 2~3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yogaforrest.pilates_bongseon?igsh=MWtyMXYwZnl1d2g0NA==</t>
+          <t>https://allroundfitness.kr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1381,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,12 +1395,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4006k</t>
+          <t>https://talk.naver.com/ct/wkdxhjp</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1405,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>26</v>
+        <v>267</v>
       </c>
       <c r="Q10" t="n">
-        <v>35</v>
+        <v>639</v>
       </c>
       <c r="R10" t="n">
-        <v>61</v>
+        <v>906</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,51 +1424,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>38332243</t>
+          <t>1709345373</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38332243</t>
+          <t>https://m.place.naver.com/place/1709345373</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>봄필라테스</t>
+          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bom_pila@naver.com</t>
+          <t>allround_fitness@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1366-5608</t>
+          <t>0507-1461-2096</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>광주 서구 풍금로151번길 6-2 연수빌딩 5층</t>
+          <t>광주 북구 북문대로 184 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_aYxjrn/chat</t>
+          <t>http://pf.kakao.com/_GRzxen/chat</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1489,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w04k3a0</t>
+          <t>https://talk.naver.com/ct/we94hjj</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>23</v>
+        <v>521</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>291</v>
       </c>
       <c r="R11" t="n">
-        <v>36</v>
+        <v>812</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,51 +1522,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2028446140</t>
+          <t>1509126970</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2028446140</t>
+          <t>https://m.place.naver.com/place/1509126970</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24시 헬스 PT 제로백피트니스 상무지구점</t>
+          <t>레벨업피트니스 헬스&amp;PT 첨단점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>zeroback2022@naver.com</t>
+          <t>wjddbqls0383@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1490-0243</t>
+          <t>0507-1317-9336</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>광주 서구 상무중앙로 7 8층 802호</t>
+          <t>광주 광산구 첨단중앙로124번길 79 2층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223830063211</t>
+          <t>https://blog.naver.com/wjddbqls0383</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1582,14 +1586,10 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5yb72</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1597,17 +1597,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>316</v>
+        <v>747</v>
       </c>
       <c r="Q12" t="n">
-        <v>614</v>
+        <v>1081</v>
       </c>
       <c r="R12" t="n">
-        <v>930</v>
+        <v>1828</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1616,17 +1616,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1013874419</t>
+          <t>1078877238</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013874419</t>
+          <t>https://m.place.naver.com/place/1078877238</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/광주_PT.xlsx
+++ b/naver-place-crawler/results_health/광주_PT.xlsx
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -1152,29 +1152,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WE휘트니스 헬스 PT 필라테스 상무점</t>
+          <t>에스짐24시피트니스 진월점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>we_fitness@naver.com</t>
+          <t>sgym3@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1388-6900</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주 서구 마륵복개로 91</t>
+          <t>광주 남구 서문대로 665 6층 SGYM 진월점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_wefit_sangmu/</t>
+          <t>https://blog.naver.com/sgym3/223208188125</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4tqh8</t>
+          <t>https://talk.naver.com/ct/w4620r</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>302</v>
+        <v>411</v>
       </c>
       <c r="Q8" t="n">
-        <v>835</v>
+        <v>401</v>
       </c>
       <c r="R8" t="n">
-        <v>1137</v>
+        <v>812</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>36670044</t>
+          <t>1264832152</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36670044</t>
+          <t>https://m.place.naver.com/place/1264832152</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1245,39 +1241,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>봄필라테스</t>
+          <t>WE휘트니스 헬스 PT 필라테스 상무점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bom_pila@naver.com</t>
+          <t>we_fitness@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1366-5608</t>
+          <t>0507-1388-6900</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 서구 풍금로151번길 6-2 연수빌딩 5층</t>
+          <t>광주 서구 마륵복개로 91</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_aYxjrn/chat</t>
+          <t>https://www.instagram.com/_wefit_sangmu/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1297,12 +1293,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w04k3a0</t>
+          <t>https://talk.naver.com/ct/w4tqh8</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>23</v>
+        <v>302</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>835</v>
       </c>
       <c r="R9" t="n">
-        <v>36</v>
+        <v>1137</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2028446140</t>
+          <t>36670044</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2028446140</t>
+          <t>https://m.place.naver.com/place/36670044</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,39 +1339,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>요가원</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
+          <t>요가포레스트&amp;필라테스 봉선점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>allround_fitness5@naver.com</t>
+          <t>cheongdam_gwangju@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1438-7908</t>
+          <t>0507-1392-4424</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>광주 서구 운천로 23-1 2~3층</t>
+          <t>광주 남구 봉선중앙로 51 3층 301-2호 요가포레스트</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://allroundfitness.kr</t>
+          <t>https://www.instagram.com/yogaforrest.pilates_bongseon?igsh=MWtyMXYwZnl1d2g0NA==</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1385,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,12 +1391,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wkdxhjp</t>
+          <t>https://talk.naver.com/ct/w4006k</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1409,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>267</v>
+        <v>26</v>
       </c>
       <c r="Q10" t="n">
-        <v>639</v>
+        <v>35</v>
       </c>
       <c r="R10" t="n">
-        <v>906</v>
+        <v>61</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1709345373</t>
+          <t>38332243</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709345373</t>
+          <t>https://m.place.naver.com/place/38332243</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1441,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
+          <t>봄필라테스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>allround_fitness@naver.com</t>
+          <t>bom_pila@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1461-2096</t>
+          <t>0507-1366-5608</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>광주 북구 북문대로 184 2층</t>
+          <t>광주 서구 풍금로151번길 6-2 연수빌딩 5층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_GRzxen/chat</t>
+          <t>http://pf.kakao.com/_aYxjrn/chat</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1493,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/we94hjj</t>
+          <t>https://talk.naver.com/ct/w04k3a0</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>521</v>
+        <v>23</v>
       </c>
       <c r="Q11" t="n">
-        <v>291</v>
+        <v>13</v>
       </c>
       <c r="R11" t="n">
-        <v>812</v>
+        <v>36</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1509126970</t>
+          <t>2028446140</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509126970</t>
+          <t>https://m.place.naver.com/place/2028446140</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1539,39 +1535,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>레벨업피트니스 헬스&amp;PT 첨단점</t>
+          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>wjddbqls0383@naver.com</t>
+          <t>allround_fitness5@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1317-9336</t>
+          <t>0507-1438-7908</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>광주 광산구 첨단중앙로124번길 79 2층</t>
+          <t>광주 서구 운천로 23-1 2~3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wjddbqls0383</t>
+          <t>https://allroundfitness.kr</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1586,13 +1582,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wkdxhjp</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>747</v>
+        <v>267</v>
       </c>
       <c r="Q12" t="n">
-        <v>1081</v>
+        <v>639</v>
       </c>
       <c r="R12" t="n">
-        <v>1828</v>
+        <v>906</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1078877238</t>
+          <t>1709345373</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1078877238</t>
+          <t>https://m.place.naver.com/place/1709345373</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
